--- a/IzlocilniBoji/SP 2026 - izlocilni - rezultati.xlsx
+++ b/IzlocilniBoji/SP 2026 - izlocilni - rezultati.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\IzlocilniBoji\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80BC6AB-0A75-4109-881D-680015EAE9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF07BA29-4705-4F19-8B6F-3FB11DEF59F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CAFA00ED-9BA4-4C89-B4D8-E7132D9D0271}"/>
+    <workbookView xWindow="-23148" yWindow="-852" windowWidth="23256" windowHeight="13896" xr2:uid="{CAFA00ED-9BA4-4C89-B4D8-E7132D9D0271}"/>
   </bookViews>
   <sheets>
     <sheet name="Lestvica 11.07." sheetId="12" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Lestvica 11.07.'!$A$1:$BP$170</definedName>
   </definedNames>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>OSMINA FINALA</t>
   </si>
@@ -83,9 +80,6 @@
     <t>RSA</t>
   </si>
   <si>
-    <t>CAN</t>
-  </si>
-  <si>
     <t>MAR</t>
   </si>
   <si>
@@ -102,6 +96,75 @@
   </si>
   <si>
     <t>CIV</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>ŠVE</t>
+  </si>
+  <si>
+    <t>KAN</t>
+  </si>
+  <si>
+    <t>NIZ</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>HRV</t>
+  </si>
+  <si>
+    <t>ŠPA</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>SEN</t>
+  </si>
+  <si>
+    <t>JAP</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>EKV</t>
+  </si>
+  <si>
+    <t>ANG</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>AVS</t>
+  </si>
+  <si>
+    <t>EGI</t>
+  </si>
+  <si>
+    <t>ALŽ</t>
+  </si>
+  <si>
+    <t>KOL</t>
+  </si>
+  <si>
+    <t>GHA</t>
+  </si>
+  <si>
+    <t>AUT</t>
   </si>
 </sst>
 </file>
@@ -653,20 +716,59 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -674,29 +776,11 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -713,17 +797,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="107"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="107"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -743,53 +833,26 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -806,23 +869,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1135,254 +1181,298 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:68" s="22" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50"/>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
       <c r="D1"/>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
-      <c r="Z1" s="66"/>
-      <c r="AA1" s="66"/>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
-      <c r="AE1" s="66"/>
-      <c r="AF1" s="66"/>
-      <c r="AG1" s="66"/>
-      <c r="AH1" s="66"/>
-      <c r="AI1" s="66"/>
-      <c r="AJ1" s="67"/>
-      <c r="AK1" s="62" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AL1" s="63"/>
-      <c r="AM1" s="63"/>
-      <c r="AN1" s="63"/>
-      <c r="AO1" s="63"/>
-      <c r="AP1" s="63"/>
-      <c r="AQ1" s="63"/>
-      <c r="AR1" s="63"/>
-      <c r="AS1" s="63"/>
-      <c r="AT1" s="63"/>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="63"/>
-      <c r="AX1" s="63"/>
-      <c r="AY1" s="63"/>
-      <c r="AZ1" s="64"/>
-      <c r="BA1" s="51" t="s">
+      <c r="AL1" s="36"/>
+      <c r="AM1" s="36"/>
+      <c r="AN1" s="36"/>
+      <c r="AO1" s="36"/>
+      <c r="AP1" s="36"/>
+      <c r="AQ1" s="36"/>
+      <c r="AR1" s="36"/>
+      <c r="AS1" s="36"/>
+      <c r="AT1" s="36"/>
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
+      <c r="AW1" s="36"/>
+      <c r="AX1" s="36"/>
+      <c r="AY1" s="36"/>
+      <c r="AZ1" s="37"/>
+      <c r="BA1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="BB1" s="52"/>
-      <c r="BC1" s="52"/>
-      <c r="BD1" s="52"/>
-      <c r="BE1" s="52"/>
-      <c r="BF1" s="52"/>
-      <c r="BG1" s="52"/>
-      <c r="BH1" s="53"/>
-      <c r="BI1" s="41" t="s">
+      <c r="BB1" s="61"/>
+      <c r="BC1" s="61"/>
+      <c r="BD1" s="61"/>
+      <c r="BE1" s="61"/>
+      <c r="BF1" s="61"/>
+      <c r="BG1" s="61"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="BJ1" s="42"/>
-      <c r="BK1" s="42"/>
-      <c r="BL1" s="43"/>
-      <c r="BM1" s="68" t="s">
+      <c r="BJ1" s="49"/>
+      <c r="BK1" s="49"/>
+      <c r="BL1" s="50"/>
+      <c r="BM1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="BN1" s="69"/>
-      <c r="BO1" s="44" t="s">
+      <c r="BN1" s="29"/>
+      <c r="BO1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="BP1" s="45"/>
+      <c r="BP1" s="52"/>
     </row>
     <row r="2" spans="1:68" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="37" t="s">
+      <c r="F2" s="38"/>
+      <c r="G2" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="35" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="40"/>
+      <c r="M2" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="41"/>
+      <c r="O2" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="43"/>
+      <c r="U2" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="V2" s="38"/>
+      <c r="W2" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="36" t="s">
-        <v>17</v>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40" t="s">
+        <v>15</v>
       </c>
-      <c r="V2" s="36"/>
-      <c r="W2" s="48" t="s">
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH2" s="43"/>
+      <c r="AI2" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="39"/>
+      <c r="AN2" s="39"/>
+      <c r="AO2" s="40"/>
+      <c r="AP2" s="40"/>
+      <c r="AQ2" s="40"/>
+      <c r="AR2" s="40"/>
+      <c r="AS2" s="41"/>
+      <c r="AT2" s="41"/>
+      <c r="AU2" s="42"/>
+      <c r="AV2" s="42"/>
+      <c r="AW2" s="43"/>
+      <c r="AX2" s="43"/>
+      <c r="AY2" s="43"/>
+      <c r="AZ2" s="43"/>
+      <c r="BA2" s="38"/>
+      <c r="BB2" s="38"/>
+      <c r="BC2" s="40"/>
+      <c r="BD2" s="40"/>
+      <c r="BE2" s="42"/>
+      <c r="BF2" s="42"/>
+      <c r="BG2" s="43"/>
+      <c r="BH2" s="43"/>
+      <c r="BI2" s="63"/>
+      <c r="BJ2" s="63"/>
+      <c r="BK2" s="64"/>
+      <c r="BL2" s="64"/>
+      <c r="BM2" s="30"/>
+      <c r="BN2" s="30"/>
+      <c r="BO2" s="65"/>
+      <c r="BP2" s="65"/>
+    </row>
+    <row r="3" spans="1:68" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="47"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="37" t="s">
-        <v>16</v>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44" t="s">
+        <v>21</v>
       </c>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="49" t="s">
-        <v>15</v>
+      <c r="H3" s="44"/>
+      <c r="I3" s="45" t="s">
+        <v>22</v>
       </c>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="36"/>
-      <c r="AL2" s="36"/>
-      <c r="AM2" s="48"/>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="37"/>
-      <c r="AP2" s="37"/>
-      <c r="AQ2" s="37"/>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="49"/>
-      <c r="AT2" s="49"/>
-      <c r="AU2" s="34"/>
-      <c r="AV2" s="34"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="36"/>
-      <c r="BC2" s="37"/>
-      <c r="BD2" s="37"/>
-      <c r="BE2" s="34"/>
-      <c r="BF2" s="34"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="54"/>
-      <c r="BJ2" s="54"/>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="70"/>
-      <c r="BN2" s="70"/>
-      <c r="BO2" s="30"/>
-      <c r="BP2" s="30"/>
-    </row>
-    <row r="3" spans="1:68" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="61"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="45"/>
+      <c r="K3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32" t="s">
-        <v>14</v>
+      <c r="L3" s="45"/>
+      <c r="M3" s="26" t="s">
+        <v>25</v>
       </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="33"/>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="31"/>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="31"/>
-      <c r="AN3" s="31"/>
-      <c r="AO3" s="32"/>
-      <c r="AP3" s="32"/>
-      <c r="AQ3" s="32"/>
-      <c r="AR3" s="32"/>
-      <c r="AS3" s="33"/>
-      <c r="AT3" s="33"/>
-      <c r="AU3" s="33"/>
-      <c r="AV3" s="33"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="28"/>
-      <c r="BD3" s="28"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="38"/>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="39"/>
-      <c r="BL3" s="39"/>
-      <c r="BM3" s="71"/>
-      <c r="BN3" s="71"/>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="40"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="27"/>
+      <c r="U3" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="44"/>
+      <c r="W3" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF3" s="26"/>
+      <c r="AG3" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="44"/>
+      <c r="AL3" s="44"/>
+      <c r="AM3" s="44"/>
+      <c r="AN3" s="44"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="45"/>
+      <c r="AR3" s="45"/>
+      <c r="AS3" s="26"/>
+      <c r="AT3" s="26"/>
+      <c r="AU3" s="26"/>
+      <c r="AV3" s="26"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="69"/>
+      <c r="BB3" s="69"/>
+      <c r="BC3" s="70"/>
+      <c r="BD3" s="70"/>
+      <c r="BE3" s="71"/>
+      <c r="BF3" s="71"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="66"/>
+      <c r="BJ3" s="66"/>
+      <c r="BK3" s="67"/>
+      <c r="BL3" s="67"/>
+      <c r="BM3" s="31"/>
+      <c r="BN3" s="31"/>
+      <c r="BO3" s="68"/>
+      <c r="BP3" s="68"/>
     </row>
     <row r="4" spans="1:68" s="22" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
@@ -13079,6 +13169,65 @@
     <sortCondition descending="1" ref="C4:C170"/>
   </sortState>
   <mergeCells count="75">
+    <mergeCell ref="BC2:BD2"/>
+    <mergeCell ref="BE2:BF2"/>
+    <mergeCell ref="BI3:BJ3"/>
+    <mergeCell ref="BK3:BL3"/>
+    <mergeCell ref="BO3:BP3"/>
+    <mergeCell ref="BG3:BH3"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="AY2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="AY3:AZ3"/>
+    <mergeCell ref="BA3:BB3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AO3:AP3"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="BI1:BL1"/>
+    <mergeCell ref="BO1:BP1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="BA1:BH1"/>
+    <mergeCell ref="BG2:BH2"/>
+    <mergeCell ref="BI2:BJ2"/>
+    <mergeCell ref="BK2:BL2"/>
+    <mergeCell ref="BO2:BP2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="S3:T3"/>
@@ -13095,65 +13244,6 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="BI1:BL1"/>
-    <mergeCell ref="BO1:BP1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="BA1:BH1"/>
-    <mergeCell ref="BG2:BH2"/>
-    <mergeCell ref="BI2:BJ2"/>
-    <mergeCell ref="BK2:BL2"/>
-    <mergeCell ref="BO2:BP2"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AO3:AP3"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="AY2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="BC2:BD2"/>
-    <mergeCell ref="BE2:BF2"/>
-    <mergeCell ref="BI3:BJ3"/>
-    <mergeCell ref="BK3:BL3"/>
-    <mergeCell ref="BO3:BP3"/>
-    <mergeCell ref="BG3:BH3"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="AY3:AZ3"/>
-    <mergeCell ref="BA3:BB3"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="BE3:BF3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
